--- a/data/WP17_sachgebiete_fraktionslos.xlsx
+++ b/data/WP17_sachgebiete_fraktionslos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t xml:space="preserve">Sachgebiet</t>
   </si>
@@ -27,9 +27,6 @@
   </si>
   <si>
     <t xml:space="preserve">Verspätet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pünktlichkeitsquote</t>
   </si>
   <si>
     <t xml:space="preserve">Innere Sicherheit</t>
@@ -659,13 +656,10 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
         <v>17</v>
@@ -679,13 +673,10 @@
       <c r="E2" t="n">
         <v>28</v>
       </c>
-      <c r="F2" t="n">
-        <v>42.8571428571429</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
         <v>17</v>
@@ -699,13 +690,10 @@
       <c r="E3" t="n">
         <v>23</v>
       </c>
-      <c r="F3" t="n">
-        <v>41.025641025641</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n">
         <v>17</v>
@@ -719,13 +707,10 @@
       <c r="E4" t="n">
         <v>29</v>
       </c>
-      <c r="F4" t="n">
-        <v>14.7058823529412</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
         <v>17</v>
@@ -739,13 +724,10 @@
       <c r="E5" t="n">
         <v>16</v>
       </c>
-      <c r="F5" t="n">
-        <v>46.6666666666667</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n">
         <v>17</v>
@@ -759,13 +741,10 @@
       <c r="E6" t="n">
         <v>10</v>
       </c>
-      <c r="F6" t="n">
-        <v>60</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
         <v>17</v>
@@ -779,13 +758,10 @@
       <c r="E7" t="n">
         <v>11</v>
       </c>
-      <c r="F7" t="n">
-        <v>47.6190476190476</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n">
         <v>17</v>
@@ -799,13 +775,10 @@
       <c r="E8" t="n">
         <v>9</v>
       </c>
-      <c r="F8" t="n">
-        <v>47.0588235294118</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>17</v>
@@ -819,13 +792,10 @@
       <c r="E9" t="n">
         <v>14</v>
       </c>
-      <c r="F9" t="n">
-        <v>17.6470588235294</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n">
         <v>17</v>
@@ -839,13 +809,10 @@
       <c r="E10" t="n">
         <v>11</v>
       </c>
-      <c r="F10" t="n">
-        <v>21.4285714285714</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n">
         <v>17</v>
@@ -859,13 +826,10 @@
       <c r="E11" t="n">
         <v>2</v>
       </c>
-      <c r="F11" t="n">
-        <v>85.7142857142857</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n">
         <v>17</v>
@@ -879,13 +843,10 @@
       <c r="E12" t="n">
         <v>1</v>
       </c>
-      <c r="F12" t="n">
-        <v>90.9090909090909</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n">
         <v>17</v>
@@ -899,13 +860,10 @@
       <c r="E13" t="n">
         <v>7</v>
       </c>
-      <c r="F13" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n">
         <v>17</v>
@@ -919,13 +877,10 @@
       <c r="E14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="n">
-        <v>77.7777777777778</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n">
         <v>17</v>
@@ -939,13 +894,10 @@
       <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F15" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n">
         <v>17</v>
@@ -959,13 +911,10 @@
       <c r="E16" t="n">
         <v>7</v>
       </c>
-      <c r="F16" t="n">
-        <v>22.2222222222222</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n">
         <v>17</v>
@@ -979,13 +928,10 @@
       <c r="E17" t="n">
         <v>2</v>
       </c>
-      <c r="F17" t="n">
-        <v>75</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n">
         <v>17</v>
@@ -999,13 +945,10 @@
       <c r="E18" t="n">
         <v>5</v>
       </c>
-      <c r="F18" t="n">
-        <v>37.5</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n">
         <v>17</v>
@@ -1019,13 +962,10 @@
       <c r="E19" t="n">
         <v>6</v>
       </c>
-      <c r="F19" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n">
         <v>17</v>
@@ -1039,13 +979,10 @@
       <c r="E20" t="n">
         <v>3</v>
       </c>
-      <c r="F20" t="n">
-        <v>62.5</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n">
         <v>17</v>
@@ -1059,13 +996,10 @@
       <c r="E21" t="n">
         <v>3</v>
       </c>
-      <c r="F21" t="n">
-        <v>57.1428571428571</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n">
         <v>17</v>
@@ -1079,13 +1013,10 @@
       <c r="E22" t="n">
         <v>1</v>
       </c>
-      <c r="F22" t="n">
-        <v>85.7142857142857</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n">
         <v>17</v>
@@ -1099,13 +1030,10 @@
       <c r="E23" t="n">
         <v>2</v>
       </c>
-      <c r="F23" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n">
         <v>17</v>
@@ -1119,13 +1047,10 @@
       <c r="E24" t="n">
         <v>3</v>
       </c>
-      <c r="F24" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n">
         <v>17</v>
@@ -1139,13 +1064,10 @@
       <c r="E25" t="n">
         <v>2</v>
       </c>
-      <c r="F25" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n">
         <v>17</v>
@@ -1159,13 +1081,10 @@
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n">
         <v>17</v>
@@ -1179,13 +1098,10 @@
       <c r="E27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" t="n">
-        <v>40</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n">
         <v>17</v>
@@ -1199,13 +1115,10 @@
       <c r="E28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n">
         <v>17</v>
@@ -1219,13 +1132,10 @@
       <c r="E29" t="n">
         <v>2</v>
       </c>
-      <c r="F29" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n">
         <v>17</v>
@@ -1239,13 +1149,10 @@
       <c r="E30" t="n">
         <v>2</v>
       </c>
-      <c r="F30" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n">
         <v>17</v>
@@ -1259,13 +1166,10 @@
       <c r="E31" t="n">
         <v>2</v>
       </c>
-      <c r="F31" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n">
         <v>17</v>
@@ -1279,13 +1183,10 @@
       <c r="E32" t="n">
         <v>3</v>
       </c>
-      <c r="F32" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n">
         <v>17</v>
@@ -1299,13 +1200,10 @@
       <c r="E33" t="n">
         <v>2</v>
       </c>
-      <c r="F33" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n">
         <v>17</v>
@@ -1319,13 +1217,10 @@
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n">
         <v>17</v>
@@ -1339,13 +1234,10 @@
       <c r="E35" t="n">
         <v>1</v>
       </c>
-      <c r="F35" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n">
         <v>17</v>
@@ -1359,13 +1251,10 @@
       <c r="E36" t="n">
         <v>1</v>
       </c>
-      <c r="F36" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n">
         <v>17</v>
@@ -1379,13 +1268,10 @@
       <c r="E37" t="n">
         <v>2</v>
       </c>
-      <c r="F37" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n">
         <v>17</v>
@@ -1399,13 +1285,10 @@
       <c r="E38" t="n">
         <v>2</v>
       </c>
-      <c r="F38" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n">
         <v>17</v>
@@ -1419,13 +1302,10 @@
       <c r="E39" t="n">
         <v>1</v>
       </c>
-      <c r="F39" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n">
         <v>17</v>
@@ -1439,13 +1319,10 @@
       <c r="E40" t="n">
         <v>2</v>
       </c>
-      <c r="F40" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n">
         <v>17</v>
@@ -1459,13 +1336,10 @@
       <c r="E41" t="n">
         <v>1</v>
       </c>
-      <c r="F41" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n">
         <v>17</v>
@@ -1479,13 +1353,10 @@
       <c r="E42" t="n">
         <v>2</v>
       </c>
-      <c r="F42" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n">
         <v>17</v>
@@ -1499,13 +1370,10 @@
       <c r="E43" t="n">
         <v>1</v>
       </c>
-      <c r="F43" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n">
         <v>17</v>
@@ -1519,13 +1387,10 @@
       <c r="E44" t="n">
         <v>2</v>
       </c>
-      <c r="F44" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n">
         <v>17</v>
@@ -1539,13 +1404,10 @@
       <c r="E45" t="n">
         <v>1</v>
       </c>
-      <c r="F45" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n">
         <v>17</v>
@@ -1559,13 +1421,10 @@
       <c r="E46" t="n">
         <v>1</v>
       </c>
-      <c r="F46" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n">
         <v>17</v>
@@ -1579,13 +1438,10 @@
       <c r="E47" t="n">
         <v>1</v>
       </c>
-      <c r="F47" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n">
         <v>17</v>
@@ -1599,13 +1455,10 @@
       <c r="E48" t="n">
         <v>2</v>
       </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n">
         <v>17</v>
@@ -1619,13 +1472,10 @@
       <c r="E49" t="n">
         <v>2</v>
       </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n">
         <v>17</v>
@@ -1639,13 +1489,10 @@
       <c r="E50" t="n">
         <v>1</v>
       </c>
-      <c r="F50" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n">
         <v>17</v>
@@ -1659,13 +1506,10 @@
       <c r="E51" t="n">
         <v>0</v>
       </c>
-      <c r="F51" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n">
         <v>17</v>
@@ -1679,13 +1523,10 @@
       <c r="E52" t="n">
         <v>0</v>
       </c>
-      <c r="F52" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n">
         <v>17</v>
@@ -1699,13 +1540,10 @@
       <c r="E53" t="n">
         <v>1</v>
       </c>
-      <c r="F53" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n">
         <v>17</v>
@@ -1719,13 +1557,10 @@
       <c r="E54" t="n">
         <v>2</v>
       </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n">
         <v>17</v>
@@ -1739,13 +1574,10 @@
       <c r="E55" t="n">
         <v>2</v>
       </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n">
         <v>17</v>
@@ -1759,13 +1591,10 @@
       <c r="E56" t="n">
         <v>1</v>
       </c>
-      <c r="F56" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n">
         <v>17</v>
@@ -1779,13 +1608,10 @@
       <c r="E57" t="n">
         <v>1</v>
       </c>
-      <c r="F57" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n">
         <v>17</v>
@@ -1799,13 +1625,10 @@
       <c r="E58" t="n">
         <v>2</v>
       </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n">
         <v>17</v>
@@ -1819,13 +1642,10 @@
       <c r="E59" t="n">
         <v>2</v>
       </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n">
         <v>17</v>
@@ -1839,13 +1659,10 @@
       <c r="E60" t="n">
         <v>0</v>
       </c>
-      <c r="F60" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n">
         <v>17</v>
@@ -1859,13 +1676,10 @@
       <c r="E61" t="n">
         <v>0</v>
       </c>
-      <c r="F61" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n">
         <v>17</v>
@@ -1879,13 +1693,10 @@
       <c r="E62" t="n">
         <v>1</v>
       </c>
-      <c r="F62" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n">
         <v>17</v>
@@ -1899,13 +1710,10 @@
       <c r="E63" t="n">
         <v>1</v>
       </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n">
         <v>17</v>
@@ -1919,13 +1727,10 @@
       <c r="E64" t="n">
         <v>1</v>
       </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n">
         <v>17</v>
@@ -1939,13 +1744,10 @@
       <c r="E65" t="n">
         <v>1</v>
       </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n">
         <v>17</v>
@@ -1959,13 +1761,10 @@
       <c r="E66" t="n">
         <v>0</v>
       </c>
-      <c r="F66" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n">
         <v>17</v>
@@ -1979,13 +1778,10 @@
       <c r="E67" t="n">
         <v>1</v>
       </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n">
         <v>17</v>
@@ -1999,13 +1795,10 @@
       <c r="E68" t="n">
         <v>0</v>
       </c>
-      <c r="F68" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n">
         <v>17</v>
@@ -2019,13 +1812,10 @@
       <c r="E69" t="n">
         <v>0</v>
       </c>
-      <c r="F69" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n">
         <v>17</v>
@@ -2039,13 +1829,10 @@
       <c r="E70" t="n">
         <v>1</v>
       </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n">
         <v>17</v>
@@ -2059,13 +1846,10 @@
       <c r="E71" t="n">
         <v>0</v>
       </c>
-      <c r="F71" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n">
         <v>17</v>
@@ -2079,13 +1863,10 @@
       <c r="E72" t="n">
         <v>0</v>
       </c>
-      <c r="F72" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n">
         <v>17</v>
@@ -2099,13 +1880,10 @@
       <c r="E73" t="n">
         <v>1</v>
       </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n">
         <v>17</v>
@@ -2119,13 +1897,10 @@
       <c r="E74" t="n">
         <v>1</v>
       </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n">
         <v>17</v>
@@ -2139,13 +1914,10 @@
       <c r="E75" t="n">
         <v>0</v>
       </c>
-      <c r="F75" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n">
         <v>17</v>
@@ -2159,13 +1931,10 @@
       <c r="E76" t="n">
         <v>1</v>
       </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n">
         <v>17</v>
@@ -2179,13 +1948,10 @@
       <c r="E77" t="n">
         <v>1</v>
       </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n">
         <v>17</v>
@@ -2199,13 +1965,10 @@
       <c r="E78" t="n">
         <v>1</v>
       </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n">
         <v>17</v>
@@ -2219,13 +1982,10 @@
       <c r="E79" t="n">
         <v>1</v>
       </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n">
         <v>17</v>
@@ -2239,13 +1999,10 @@
       <c r="E80" t="n">
         <v>0</v>
       </c>
-      <c r="F80" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n">
         <v>17</v>
@@ -2259,13 +2016,10 @@
       <c r="E81" t="n">
         <v>1</v>
       </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n">
         <v>17</v>
@@ -2279,13 +2033,10 @@
       <c r="E82" t="n">
         <v>1</v>
       </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n">
         <v>17</v>
@@ -2299,13 +2050,10 @@
       <c r="E83" t="n">
         <v>0</v>
       </c>
-      <c r="F83" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n">
         <v>17</v>
@@ -2319,13 +2067,10 @@
       <c r="E84" t="n">
         <v>0</v>
       </c>
-      <c r="F84" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n">
         <v>17</v>
@@ -2339,13 +2084,10 @@
       <c r="E85" t="n">
         <v>0</v>
       </c>
-      <c r="F85" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n">
         <v>17</v>
@@ -2359,13 +2101,10 @@
       <c r="E86" t="n">
         <v>0</v>
       </c>
-      <c r="F86" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n">
         <v>17</v>
@@ -2379,13 +2118,10 @@
       <c r="E87" t="n">
         <v>1</v>
       </c>
-      <c r="F87" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B88" t="n">
         <v>17</v>
@@ -2399,13 +2135,10 @@
       <c r="E88" t="n">
         <v>0</v>
       </c>
-      <c r="F88" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B89" t="n">
         <v>17</v>
@@ -2419,13 +2152,10 @@
       <c r="E89" t="n">
         <v>0</v>
       </c>
-      <c r="F89" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B90" t="n">
         <v>17</v>
@@ -2439,13 +2169,10 @@
       <c r="E90" t="n">
         <v>0</v>
       </c>
-      <c r="F90" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B91" t="n">
         <v>17</v>
@@ -2459,13 +2186,10 @@
       <c r="E91" t="n">
         <v>1</v>
       </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B92" t="n">
         <v>17</v>
@@ -2479,13 +2203,10 @@
       <c r="E92" t="n">
         <v>0</v>
       </c>
-      <c r="F92" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B93" t="n">
         <v>17</v>
@@ -2499,13 +2220,10 @@
       <c r="E93" t="n">
         <v>1</v>
       </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B94" t="n">
         <v>17</v>
@@ -2519,13 +2237,10 @@
       <c r="E94" t="n">
         <v>0</v>
       </c>
-      <c r="F94" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B95" t="n">
         <v>17</v>
@@ -2539,13 +2254,10 @@
       <c r="E95" t="n">
         <v>0</v>
       </c>
-      <c r="F95" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B96" t="n">
         <v>17</v>
@@ -2558,9 +2270,6 @@
       </c>
       <c r="E96" t="n">
         <v>0</v>
-      </c>
-      <c r="F96" t="n">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2797,13 +2506,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781DABF1-89A2-485A-A4B2-5759C0E99E9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8B925F7-8AA8-4143-BAB7-FF94EA4F1BA7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C55CB536-612E-48F1-8D87-E2EE05C79170}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D885DC31-6A27-4F68-AA54-55BC8A428846}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82A114F-73A4-4DFE-891E-2AC70CCAAF14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E342A84-0FD8-40CA-B8E5-E1907AF4F773}"/>
 </file>